--- a/coaching_forms/013_parent_coaching_intake_survey--coaching_forms.xlsx
+++ b/coaching_forms/013_parent_coaching_intake_survey--coaching_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1110,8 +1110,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="47" customWidth="1" min="2" max="2"/>
-    <col width="47" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_10,_'label':_'one'}</t>
+          <t>one</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 10, 'label': 'One'}</t>
+          <t>One</t>
         </is>
       </c>
     </row>
@@ -1156,12 +1156,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_11,_'label':_'two_or_more'}</t>
+          <t>two_or_more</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 11, 'label': 'Two or more'}</t>
+          <t>Two or more</t>
         </is>
       </c>
     </row>
@@ -1173,12 +1173,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_20,_'label':_'one_on_one_coaching'}</t>
+          <t>one_on_one_coaching</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 20, 'label': 'One on one coaching'}</t>
+          <t>One on one coaching</t>
         </is>
       </c>
     </row>
@@ -1190,12 +1190,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_21,_'label':_'group_coaching'}</t>
+          <t>group_coaching</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 21, 'label': 'Group coaching'}</t>
+          <t>Group coaching</t>
         </is>
       </c>
     </row>
@@ -1207,12 +1207,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_22,_'label':_'other_(please_specify)'}</t>
+          <t>other_(please_specify)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 22, 'label': 'Other (please specify)'}</t>
+          <t>Other (please specify)</t>
         </is>
       </c>
     </row>
@@ -1224,12 +1224,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_30,_'label':_'parent_and_counselor'}</t>
+          <t>parent_and_counselor</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 30, 'label': 'Parent and Counselor'}</t>
+          <t>Parent and Counselor</t>
         </is>
       </c>
     </row>
@@ -1241,12 +1241,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_31,_'label':_'parent_and_parent'}</t>
+          <t>parent_and_parent</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 31, 'label': 'Parent and Parent'}</t>
+          <t>Parent and Parent</t>
         </is>
       </c>
     </row>
@@ -1258,12 +1258,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_32,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 32, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1275,12 +1275,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_40,_'label':_'goal_one'}</t>
+          <t>goal_one</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 40, 'label': 'Goal One'}</t>
+          <t>Goal One</t>
         </is>
       </c>
     </row>
@@ -1292,12 +1292,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_41,_'label':_'goal_two'}</t>
+          <t>goal_two</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 41, 'label': 'Goal Two'}</t>
+          <t>Goal Two</t>
         </is>
       </c>
     </row>
@@ -1309,12 +1309,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_42,_'label':_'goal_three'}</t>
+          <t>goal_three</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 42, 'label': 'Goal Three'}</t>
+          <t>Goal Three</t>
         </is>
       </c>
     </row>
@@ -1326,12 +1326,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_50,_'label':_'parent_expectations'}</t>
+          <t>parent_expectations</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 50, 'label': 'Parent Expectations'}</t>
+          <t>Parent Expectations</t>
         </is>
       </c>
     </row>
@@ -1343,12 +1343,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_51,_'label':_'parent_goals'}</t>
+          <t>parent_goals</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 51, 'label': 'Parent Goals'}</t>
+          <t>Parent Goals</t>
         </is>
       </c>
     </row>
@@ -1360,12 +1360,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_60,_'label':_'emergency_contact'}</t>
+          <t>emergency_contact</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 60, 'label': 'Emergency Contact'}</t>
+          <t>Emergency Contact</t>
         </is>
       </c>
     </row>
@@ -1377,12 +1377,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_61,_'label':_'family_member'}</t>
+          <t>family_member</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 61, 'label': 'Family Member'}</t>
+          <t>Family Member</t>
         </is>
       </c>
     </row>
